--- a/REKAP NILAIAN ASTS - Personal Branding XI DKV 2026-2027.xlsx
+++ b/REKAP NILAIAN ASTS - Personal Branding XI DKV 2026-2027.xlsx
@@ -1,105 +1,105 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. REKAP NILAI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. NILAI KOMPONEN" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Wahdan Sapari" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Ahmad Fauzi" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Qiandra Kaizar Nahari" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Ilma Latifah" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Sopa Anidatul Aisah" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Jajang M Husni Mubarok" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Silvi Budia Putri" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Nurjihan" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Dede Aprilia Kartika" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Putri Intan Nuraeni" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Intan Widiyanti" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Safinah Syara Garini" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Quinsya Rahmanesa Sole" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Jihan Shafira Kean Put" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Dhea Eka Khoerunnisa" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Wulan Sundari" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Wilda Azkia" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Muhamad Diaz Pirdaus" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Rizky Muhammad Regal S" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Khanza Nuraeni" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Ceisha Sinthia" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Selvi Sifa Urizqi" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Azmi Anugrah" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Indri Fitriyani" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Meisya Fakhriyah" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - M Reza Huafah" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Syiva Widiyana Agustin" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Meylan Meliyanti Anast" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Putri Utami" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Kamila Apriliani" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Yayu Astia" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Wina Afriliani" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Jajang Nurjaman" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Shandika Revi Shafarud" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Ai Tito" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Merlin Aznika" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Neng Sri Rahayu" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Sindia Saputri" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Mutia Anita Sari" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Harum Nuraulia Sri Kam" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Azzahra Qyasimah" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Aupa Aznia" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Alya Nuraeni" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Siti Jenab" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Wildan" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Debi Lestari" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Hasni Sapa Al Maira" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Ilfa Alifiana Khoeruni" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Dira Rahmawati" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Nazma Kayva Gasani" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Riana Sanjaya" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Nazwa Nur Aisyah" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Ai Cinta Lestari" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Tira Fadila" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Ai Nurawaliah Al Zahra" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Ai Imas" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Syifa Haira" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Rismayanti" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Moh Pikri" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Sumiyati" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Ajeng Dwi Raissa Fitri" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Sri Ayu Wahyuni" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Risma Saparani" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Zahratul Ayesa Aulia" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Gadna Widiatni" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Devina Nayyra Fitriani" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Sulistiawati" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Sechan Khalifatunnisa" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Fitriyani" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Syabina Ayat El Akhros" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Siti Rahma Silpiana" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Teni Damayanti" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Siti Khoiriyah" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Aqila Nazil Falaq" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Resti Nurul Fadila" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Neng Oktavia Putri Agu" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Fahmi Ahmad Ramdan Alf" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Nadira Mega Rizkia" sheetId="80" state="visible" r:id="rId80"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Rita Pebriyani" sheetId="81" state="visible" r:id="rId81"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Ai Siti Muslimah" sheetId="82" state="visible" r:id="rId82"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Nani Yuliyani" sheetId="83" state="visible" r:id="rId83"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Amira Nur Aulia" sheetId="84" state="visible" r:id="rId84"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Raira Putri" sheetId="85" state="visible" r:id="rId85"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Kaila Aropatilah" sheetId="86" state="visible" r:id="rId86"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Nuri Meitri Aeni" sheetId="87" state="visible" r:id="rId87"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail - Nazwa Kurnia" sheetId="88" state="visible" r:id="rId88"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. REKAP KETIDAKLENGKAPAN" sheetId="89" state="visible" r:id="rId89"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. CEK MANUAL GURU" sheetId="90" state="visible" r:id="rId90"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. DATA REKAPAN" sheetId="91" state="visible" r:id="rId91"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. NILAI TAMBAHAN RESOLUSI" sheetId="92" state="visible" r:id="rId92"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. METODE &amp; RUBRIK" sheetId="93" state="visible" r:id="rId93"/>
+    <sheet name="1. REKAP NILAI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2. NILAI KOMPONEN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Detail - Wahdan Sapari" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Detail - Ahmad Fauzi" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Detail - Qiandra Kaizar Nahari" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Detail - Ilma Latifah" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Detail - Sopa Anidatul Aisah" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Detail - Jajang M Husni Mubarok" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Detail - Silvi Budia Putri" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Detail - Nurjihan" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Detail - Dede Aprilia Kartika" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Detail - Putri Intan Nuraeni" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Detail - Intan Widiyanti" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Detail - Safinah Syara Garini" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Detail - Quinsya Rahmanesa Sole" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Detail - Jihan Shafira Kean Put" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Detail - Dhea Eka Khoerunnisa" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Detail - Wulan Sundari" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Detail - Wilda Azkia" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Detail - Muhamad Diaz Pirdaus" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Detail - Rizky Muhammad Regal S" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Detail - Khanza Nuraeni" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Detail - Ceisha Sinthia" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Detail - Selvi Sifa Urizqi" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Detail - Azmi Anugrah" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Detail - Indri Fitriyani" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Detail - Meisya Fakhriyah" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Detail - M Reza Huafah" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Detail - Syiva Widiyana Agustin" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Detail - Meylan Meliyanti Anast" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Detail - Putri Utami" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Detail - Kamila Apriliani" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Detail - Yayu Astia" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Detail - Wina Afriliani" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Detail - Jajang Nurjaman" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Detail - Shandika Revi Shafarud" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Detail - Ai Tito" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Detail - Merlin Aznika" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Detail - Neng Sri Rahayu" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Detail - Sindia Saputri" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Detail - Mutia Anita Sari" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Detail - Harum Nuraulia Sri Kam" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="Detail - Azzahra Qyasimah" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="Detail - Aupa Aznia" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="Detail - Alya Nuraeni" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="Detail - Siti Jenab" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="Detail - Wildan" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="Detail - Debi Lestari" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="Detail - Hasni Sapa Al Maira" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="Detail - Ilfa Alifiana Khoeruni" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="Detail - Dira Rahmawati" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="Detail - Nazma Kayva Gasani" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="Detail - Riana Sanjaya" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="Detail - Nazwa Nur Aisyah" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="Detail - Ai Cinta Lestari" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="Detail - Tira Fadila" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="Detail - Ai Nurawaliah Al Zahra" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="Detail - Ai Imas" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="Detail - Syifa Haira" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="Detail - Rismayanti" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="Detail - Moh Pikri" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="Detail - Sumiyati" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="Detail - Ajeng Dwi Raissa Fitri" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="Detail - Sri Ayu Wahyuni" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="Detail - Risma Saparani" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="Detail - Zahratul Ayesa Aulia" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="Detail - Gadna Widiatni" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="Detail - Devina Nayyra Fitriani" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="Detail - Sulistiawati" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="Detail - Sechan Khalifatunnisa" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="Detail - Fitriyani" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="Detail - Syabina Ayat El Akhros" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="Detail - Siti Rahma Silpiana" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="Detail - Teni Damayanti" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="Detail - Siti Khoiriyah" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="Detail - Aqila Nazil Falaq" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="Detail - Resti Nurul Fadila" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet name="Detail - Neng Oktavia Putri Agu" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="Detail - Fahmi Ahmad Ramdan Alf" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet name="Detail - Nadira Mega Rizkia" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet name="Detail - Rita Pebriyani" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet name="Detail - Ai Siti Muslimah" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet name="Detail - Nani Yuliyani" sheetId="83" state="visible" r:id="rId83"/>
+    <sheet name="Detail - Amira Nur Aulia" sheetId="84" state="visible" r:id="rId84"/>
+    <sheet name="Detail - Raira Putri" sheetId="85" state="visible" r:id="rId85"/>
+    <sheet name="Detail - Kaila Aropatilah" sheetId="86" state="visible" r:id="rId86"/>
+    <sheet name="Detail - Nuri Meitri Aeni" sheetId="87" state="visible" r:id="rId87"/>
+    <sheet name="Detail - Nazwa Kurnia" sheetId="88" state="visible" r:id="rId88"/>
+    <sheet name="3. REKAP KETIDAKLENGKAPAN" sheetId="89" state="visible" r:id="rId89"/>
+    <sheet name="4. CEK MANUAL GURU" sheetId="90" state="visible" r:id="rId90"/>
+    <sheet name="5. DATA REKAPAN" sheetId="91" state="visible" r:id="rId91"/>
+    <sheet name="7. NILAI TAMBAHAN RESOLUSI" sheetId="92" state="visible" r:id="rId92"/>
+    <sheet name="6. METODE &amp; RUBRIK" sheetId="93" state="visible" r:id="rId93"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/REKAP NILAIAN ASTS - Personal Branding XI DKV 2026-2027.xlsx
+++ b/REKAP NILAIAN ASTS - Personal Branding XI DKV 2026-2027.xlsx
@@ -109,7 +109,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -161,6 +161,10 @@
       <i val="1"/>
       <color rgb="00C00000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <i val="1"/>
@@ -232,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -295,10 +299,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -712,7 +717,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Sumber: rekapan Google Form (18 kiriman) + akses langsung ke Blogger + 119 berkas gambar (OCR &amp; dimensi piksel asli)</t>
+          <t>Sumber: rekapan Google Form (86 kiriman) + akses langsung ke Blogger + 555 berkas gambar (OCR &amp; dimensi piksel asli)</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2075,7 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>0 dari 5 gambar &gt;=1000px (maks 320)</t>
+          <t>0 dari 5 gambar &gt;=1000px (maks 400)</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
@@ -22654,7 +22659,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Tidak ada gambar &gt;= 1000 px (maks 320 px). TIDAK ada potongan nilai - resolusi rendah tetap diperbolehkan.</t>
+          <t>Tidak ada gambar &gt;= 1000 px (maks 400 px). TIDAK ada potongan nilai - resolusi rendah tetap diperbolehkan.</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
@@ -72408,7 +72413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -72500,7 +72505,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>JIHAN SHAFIRA KEAN P.M.</t>
+          <t>JIHAN SHAFIRA KEAN PUTRI MULYADI</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -72799,7 +72804,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>JIHAN SHAFIRA KEAN P.M.</t>
+          <t>JIHAN SHAFIRA KEAN PUTRI MULYADI</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -72861,6 +72866,236 @@
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>MUHAMAD DIAZ PIRDAUS</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Orisinalitas heading '{Monogram SSG}'</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Heading yang sama persis muncul pada 4 kiriman: MUHAMAD DIAZ PIRDAUS, NAZMA KAYVA GASANI, TENI DAMAYANTI, RESTI NURUL FADILA. Perlu klarifikasi orisinalitas dari siswa.</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>NAZWA KAYVA GASANI</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Orisinalitas heading '{Monogram SSG}'</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Lihat butir MUHAMAD DIAZ PIRDAUS - heading identik pada 4 kiriman.</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>TENI DAMAYANTI</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Orisinalitas heading '{Monogram SSG}'</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Lihat butir MUHAMAD DIAZ PIRDAUS - heading identik pada 4 kiriman.</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>RESTI NURUL FADILA</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Orisinalitas heading '{Monogram SSG}'</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Lihat butir MUHAMAD DIAZ PIRDAUS - heading identik pada 4 kiriman.</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>CEISHA SINTHIA</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Kirim link artikel publik</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Link yang masuk adalah URL editor Blogger (redirect login Google). Nilai 0 karena karya tidak dapat diverifikasi.</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>SINDIA SAPUTRI</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Kirim link artikel publik</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Link yang masuk adalah URL editor Blogger (redirect login Google). Nilai 0 karena karya tidak dapat diverifikasi.</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>SITI JENAB</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Kirim link artikel publik</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Link yang masuk adalah URL editor Blogger (redirect login Google). Nilai 0 karena karya tidak dapat diverifikasi.</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>NAZWA KURNIA</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Kirim link artikel publik</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Link yang masuk adalah URL editor Blogger (redirect login Google). Nilai 0 karena karya tidak dapat diverifikasi.</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>RISMA SAPARANI</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Kirim link artikel publik yang aktif</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Link mengembalikan HTTP 404. Nilai 0 karena karya tidak dapat diverifikasi.</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>NURI MEITRI AENI</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Kirim link artikel publik yang aktif</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Link mengembalikan HTTP 404. Nilai 0 karena karya tidak dapat diverifikasi.</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -73086,11 +73321,7 @@
           <t>AKTIF (HTTP 200)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Heading '{Monogram SSG}' - teks milik siswa lain</t>
-        </is>
-      </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n">
@@ -73245,7 +73476,11 @@
           <t>AKTIF (HTTP 200)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Judul artikel 'ASTS KOMPETENSI AI DKV - SMKN 9 GARUT' - perlu verifikasi identitas</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n">
@@ -73495,7 +73730,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Heading '{Monogram SSG}' - teks milik siswa lain</t>
+          <t>Heading '{Monogram SSG}' - teks yang sama juga muncul di 3 kiriman lain</t>
         </is>
       </c>
     </row>
@@ -73585,9 +73820,9 @@
           <t>https://www.blogger.com/blog/post/edit/1670849221285353060/1910546013362529910</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>AKTIF (HTTP 200)</t>
+      <c r="F25" s="30" t="inlineStr">
+        <is>
+          <t>TIDAK AKSES - URL editor Blogger (redirect login Google)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
@@ -73621,11 +73856,7 @@
           <t>AKTIF (HTTP 200)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Heading '{Monogram SSG}' - teks milik siswa lain</t>
-        </is>
-      </c>
+      <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="18" t="n">
@@ -73656,7 +73887,11 @@
           <t>AKTIF (HTTP 200)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Judul artikel 'UJI KOPETENSI PROMTPTING AI DKV' - perlu verifikasi identitas</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
@@ -74116,9 +74351,9 @@
           <t>https://www.blogger.com/blog/post/edit/5651927338979487239/2915016707387024877</t>
         </is>
       </c>
-      <c r="F42" s="18" t="inlineStr">
-        <is>
-          <t>AKTIF (HTTP 200)</t>
+      <c r="F42" s="30" t="inlineStr">
+        <is>
+          <t>TIDAK AKSES - URL editor Blogger (redirect login Google)</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
@@ -74152,7 +74387,11 @@
           <t>AKTIF (HTTP 200)</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Page title 'ASTS personal branding nama Mutia' - nama pada judul tidak lengkap</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="n">
@@ -74302,9 +74541,9 @@
           <t>https://www.blogger.com/blog/post/edit/6008126407079284721/1930981037777581071</t>
         </is>
       </c>
-      <c r="F48" s="18" t="inlineStr">
-        <is>
-          <t>AKTIF (HTTP 200)</t>
+      <c r="F48" s="30" t="inlineStr">
+        <is>
+          <t>TIDAK AKSES - URL editor Blogger (redirect login Google)</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
@@ -74493,7 +74732,11 @@
           <t>AKTIF (HTTP 200)</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Heading '{Monogram SSG}' - teks yang sama juga muncul di 3 kiriman lain</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="18" t="n">
@@ -74891,9 +75134,9 @@
           <t>https://27-01-2010.blogspot.com/2026/10/personal-branding-risma-saparani-xi-dkv-2.html</t>
         </is>
       </c>
-      <c r="F67" s="18" t="inlineStr">
-        <is>
-          <t>AKTIF (HTTP 200)</t>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>TIDAK AKSES - HTTP 404</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
@@ -75175,7 +75418,11 @@
           <t>AKTIF (HTTP 200)</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Heading '{Monogram SSG}' - teks yang sama juga muncul di 3 kiriman lain</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="18" t="n">
@@ -75268,7 +75515,11 @@
           <t>AKTIF (HTTP 200)</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Heading '{Monogram SSG}' - teks yang sama juga muncul di 3 kiriman lain</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="18" t="n">
@@ -75573,9 +75824,9 @@
           <t>https://nurimeitriii.blogspot.com/2026/10/identity-essenncenuri-mei-tri-aeni.html</t>
         </is>
       </c>
-      <c r="F89" s="18" t="inlineStr">
-        <is>
-          <t>AKTIF (HTTP 200)</t>
+      <c r="F89" s="30" t="inlineStr">
+        <is>
+          <t>TIDAK AKSES - HTTP 404</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr"/>
@@ -75604,9 +75855,9 @@
           <t>https://www.blogger.com/blog/post/edit/9148967484819656515/7200518875422246523</t>
         </is>
       </c>
-      <c r="F90" s="18" t="inlineStr">
-        <is>
-          <t>AKTIF (HTTP 200)</t>
+      <c r="F90" s="30" t="inlineStr">
+        <is>
+          <t>TIDAK AKSES - URL editor Blogger (redirect login Google)</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr"/>
@@ -75642,7 +75893,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>REVISI RUBRIK KE-3: nilai tambah resolusi DITURUNKAN agar pengaruhnya kecil. Resolusi TIDAK menjadi potongan nilai - resolusi tetap diperbolehkan. Visual beresolusi &gt; 1000 px hanya mendapat NILAI TAMBAHAN, maksimal +1,0 poin.</t>
         </is>
@@ -76165,7 +76416,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -76174,7 +76425,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Tidak ada gambar &gt;= 1000 px (maks 320 px). TIDAK ada potongan nilai - resolusi rendah tetap diperbolehkan.</t>
+          <t>Tidak ada gambar &gt;= 1000 px (maks 400 px). TIDAK ada potongan nilai - resolusi rendah tetap diperbolehkan.</t>
         </is>
       </c>
     </row>
@@ -78253,7 +78504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -78268,7 +78519,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>REVISI RUBRIK KE-3 (1 Oktober 2026)</t>
         </is>
@@ -78280,7 +78531,7 @@
           <t>Nilai tambah resolusi</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>Diturunkan agar pengaruhnya kecil: +1,0 / +0,7 / +0,4 / 0 (maksimal +1,0 poin, bukan +3).</t>
         </is>
@@ -78292,7 +78543,7 @@
           <t>Resolusi rendah</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>TIDAK menjadi potongan nilai. Resolusi tetap diperbolehkan.</t>
         </is>
@@ -78304,7 +78555,7 @@
           <t>Nilai Akhir</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Nilai Rubrik (0-100) + Nilai Tambah Resolusi, dibatasi maksimum 100.</t>
         </is>
@@ -78316,14 +78567,14 @@
           <t>Dampak</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>18 siswa dihitung ulang. Tidak ada nilai turun; selisih hanya pada 6 siswa yang mendapat nilai tambah.</t>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>18 siswa dihitung ulang saat revisi ini diterapkan (1 Oktober 2026). Tidak ada nilai turun; selisih hanya pada 6 siswa yang mendapat nilai tambah.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>REVISI RUBRIK KE-2 (1 Oktober 2026)</t>
         </is>
@@ -78335,7 +78586,7 @@
           <t>Resolusi rendah</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>TIDAK lagi menjadi potongan nilai. Resolusi tetap diperbolehkan.</t>
         </is>
@@ -78347,14 +78598,14 @@
           <t>Nilai tambah resolusi</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Diperkenalkan: visual &gt; 1000 px mendapat nilai tambahan (skala +3/+2/+1, kemudian diturunkan pada Revisi-3).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>REVISI RUBRIK KE-1 (1 Oktober 2026)</t>
         </is>
@@ -78366,7 +78617,7 @@
           <t>1. Written 'by Nama Siswa'</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>TIDAK lagi syarat. Yang wajib: NAMA SISWA tercantum pada branding/logo.</t>
         </is>
@@ -78378,7 +78629,7 @@
           <t>2. AI Mascot Character</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>WAJIB: Mascot Full Body. OPSIONAL: Mascot Portrait &amp; Mascot Bersama Logo.</t>
         </is>
@@ -78390,7 +78641,7 @@
           <t>3. Shotlist</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Boleh dalam bentuk TABEL maupun GAMBAR. Minimal 10 shot tetap berlaku.</t>
         </is>
@@ -78402,14 +78653,14 @@
           <t>Dampak</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Nilai seluruh siswa DIHITUNG ULANG. Tidak ada siswa yang mengunggah ulang (0 perubahan data).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>METODE VERIFIKASI</t>
         </is>
@@ -78421,9 +78672,9 @@
           <t>Sumber 1</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
-        <is>
-          <t>Rekapan pengumpulan Google Form: 18 kiriman (nama, kelas, link, timestamp).</t>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>Rekapan pengumpulan Google Form: 86 kiriman (nama, kelas, link, timestamp).</t>
         </is>
       </c>
     </row>
@@ -78433,9 +78684,9 @@
           <t>Sumber 2</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
-        <is>
-          <t>Halaman Blogger publik diakses langsung satu per satu (HTTP 200 untuk 18 dari 18).</t>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Halaman Blogger diakses langsung satu per satu. 80 dari 86 dapat diakses publik; 4 siswa mengirim URL editor Blogger (mengarah ke halaman login Google) dan 2 link mengembalikan HTTP 404.</t>
         </is>
       </c>
     </row>
@@ -78445,9 +78696,9 @@
           <t>Sumber 3</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
-        <is>
-          <t>119 berkas gambar diunduh dari Blogger dan diperiksa dengan OCR (Apple Vision) + dimensi piksel asli.</t>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>555 berkas gambar terukur (dimensi piksel asli) dan diperiksa dengan OCR (Apple Vision). 6 siswa tidak memiliki gambar yang dapat diukur karena link tidak dapat diakses.</t>
         </is>
       </c>
     </row>
@@ -78457,14 +78708,14 @@
           <t>Sumber 4</t>
         </is>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Teks artikel, tabel, heading, dan label/tag Blogger.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>KETERBATASAN PENTING</t>
         </is>
@@ -78476,7 +78727,7 @@
           <t>Vision</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Ases TIDAK memiliki kemampuan melihat gambar. Verifikasi visual memakai OCR + dimensi piksel asli.</t>
         </is>
@@ -78488,7 +78739,7 @@
           <t>Terverifikasi</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Jumlah baris tabel, jumlah kata, jumlah berkas gambar, orientasi gambar, teks dalam gambar, label/tag.</t>
         </is>
@@ -78500,7 +78751,7 @@
           <t>Tidak terverifikasi</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Jumlah unit di dalam satu gambar kolase, bila label/penomoran tidak terbaca OCR. Ditulis TIDAK DAPAT DIVERIFIKASI.</t>
         </is>
@@ -78512,14 +78763,14 @@
           <t>Aturan</t>
         </is>
       </c>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Tidak ada nilai diberikan berdasarkan asumsi. Komponen yang tidak ditemukan ditulis 'Tidak ditemukan pada hasil pengumpulan'.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>ATURAN PENILAIAN</t>
         </is>
@@ -78531,7 +78782,7 @@
           <t>Rumus</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Nilai komponen = (Skor / 4) x Bobot. Total = jumlah seluruh nilai komponen. Skala 0-4.</t>
         </is>
@@ -78543,7 +78794,7 @@
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>90-100 Sangat Baik | 80-89 Baik | 70-79 Cukup | &lt;70 Perlu Perbaikan.</t>
         </is>
@@ -78555,14 +78806,14 @@
           <t>Waktu</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
-        <is>
-          <t>Seluruh 18 kiriman sebelum batas 2 Oktober 2026 23.59 WIB. Waktu TIDAK mengubah skor kualitas.</t>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Seluruh 86 kiriman sebelum batas 2 Oktober 2026 23.59 WIB. Waktu TIDAK mengubah skor kualitas.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="31" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>BOBOT KOMPONEN</t>
         </is>
@@ -78574,7 +78825,7 @@
           <t>Penamaan Judul &amp; Identitas</t>
         </is>
       </c>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>bobot 5 poin</t>
         </is>
@@ -78586,7 +78837,7 @@
           <t>Personal Branding &amp; Logo</t>
         </is>
       </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>bobot 12 poin</t>
         </is>
@@ -78598,7 +78849,7 @@
           <t>Moodboard</t>
         </is>
       </c>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>bobot 8 poin</t>
         </is>
@@ -78610,7 +78861,7 @@
           <t>Mockup Branding</t>
         </is>
       </c>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="B40" s="33" t="inlineStr">
         <is>
           <t>bobot 10 poin</t>
         </is>
@@ -78622,7 +78873,7 @@
           <t>Naskah Iklan</t>
         </is>
       </c>
-      <c r="B41" s="32" t="inlineStr">
+      <c r="B41" s="33" t="inlineStr">
         <is>
           <t>bobot 8 poin</t>
         </is>
@@ -78634,7 +78885,7 @@
           <t>Storyline</t>
         </is>
       </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>bobot 8 poin</t>
         </is>
@@ -78646,7 +78897,7 @@
           <t>Shotlist</t>
         </is>
       </c>
-      <c r="B43" s="32" t="inlineStr">
+      <c r="B43" s="33" t="inlineStr">
         <is>
           <t>bobot 10 poin</t>
         </is>
@@ -78658,7 +78909,7 @@
           <t>Storyboard</t>
         </is>
       </c>
-      <c r="B44" s="32" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>bobot 10 poin</t>
         </is>
@@ -78670,7 +78921,7 @@
           <t>AI Mascot Character</t>
         </is>
       </c>
-      <c r="B45" s="32" t="inlineStr">
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>bobot 8 poin</t>
         </is>
@@ -78682,7 +78933,7 @@
           <t>Prompt &amp; Dokumentasi AI</t>
         </is>
       </c>
-      <c r="B46" s="32" t="inlineStr">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>bobot 7 poin</t>
         </is>
@@ -78694,7 +78945,7 @@
           <t>Portfolio Blogger</t>
         </is>
       </c>
-      <c r="B47" s="32" t="inlineStr">
+      <c r="B47" s="33" t="inlineStr">
         <is>
           <t>bobot 10 poin</t>
         </is>
@@ -78706,7 +78957,7 @@
           <t>Kreativitas &amp; Profesionalisme</t>
         </is>
       </c>
-      <c r="B48" s="32" t="inlineStr">
+      <c r="B48" s="33" t="inlineStr">
         <is>
           <t>bobot 4 poin</t>
         </is>
@@ -78718,14 +78969,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B50" s="32" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr">
         <is>
           <t>100 poin</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31" t="inlineStr">
+      <c r="A52" s="32" t="inlineStr">
         <is>
           <t>CATATAN PENTING UNTUK GURU</t>
         </is>
@@ -78737,7 +78988,7 @@
           <t>Cek manual</t>
         </is>
       </c>
-      <c r="B53" s="32" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>Lihat sheet '4. CEK MANUAL GURU' untuk butir yang tidak dapat dipastikan.</t>
         </is>
@@ -78749,9 +79000,21 @@
           <t>Data rekapan</t>
         </is>
       </c>
-      <c r="B54" s="32" t="inlineStr">
-        <is>
-          <t>Rekapan Google Form berisi 18 kiriman. Tiga nama tidak lagi tercatat pada Form: ADE SAHRUL GUNAWAN, DIRA RAHMAWATI, FITRIYANI - ketiganya dikeluarkan dari penilaian atas keputusan guru.</t>
+      <c r="B54" s="33" t="inlineStr">
+        <is>
+          <t>Rekapan Google Form berisi 86 kiriman dan seluruh 86 siswa dinilai. Tidak ada siswa yang dikeluarkan dari penilaian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>Nilai 0</t>
+        </is>
+      </c>
+      <c r="B55" s="33" t="inlineStr">
+        <is>
+          <t>6 siswa bernilai 0 karena karya tidak dapat diverifikasi, bukan karena karya kosong: 4 siswa mengirim URL editor Blogger (CEISHA SINTHIA, SINDIA SAPUTRI, SITI JENAB, NAZWA KURNIA) dan 2 link mengembalikan HTTP 404 (RISMA SAPARANI, NURI MEITRI AENI).</t>
         </is>
       </c>
     </row>
